--- a/data/trans_dic/IP24_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que no hacen ejercicio</t>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,85; 79,3</t>
+          <t>65,74; 79,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,23; 65,12</t>
+          <t>52,62; 65,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,43; 69,36</t>
+          <t>55,73; 68,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,87; 54,77</t>
+          <t>35,15; 55,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,78; 77,3</t>
+          <t>63,71; 77,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,31; 71,73</t>
+          <t>58,13; 71,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,55; 65,71</t>
+          <t>51,2; 65,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,49; 61,88</t>
+          <t>42,84; 62,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,77; 76,24</t>
+          <t>66,11; 76,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56,69; 65,89</t>
+          <t>57,09; 66,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,6; 65,71</t>
+          <t>55,84; 65,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,48; 56,37</t>
+          <t>42,05; 56,04</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,77; 25,02</t>
+          <t>16,61; 25,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 16,11</t>
+          <t>8,76; 16,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 19,38</t>
+          <t>11,72; 19,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,7; 27,84</t>
+          <t>15,96; 27,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 25,91</t>
+          <t>17,4; 25,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,85</t>
+          <t>3,93; 8,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 16,58</t>
+          <t>10,26; 16,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 20,74</t>
+          <t>11,65; 20,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 24,12</t>
+          <t>18,01; 23,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,0</t>
+          <t>6,72; 10,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,9</t>
+          <t>11,72; 16,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,77; 22,58</t>
+          <t>15,22; 22,81</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 17,23</t>
+          <t>8,39; 17,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,42</t>
+          <t>1,98; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,46</t>
+          <t>5,14; 11,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 17,63</t>
+          <t>8,3; 17,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,08</t>
+          <t>6,35; 14,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,37</t>
+          <t>0,4; 3,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,92</t>
+          <t>2,15; 6,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 18,34</t>
+          <t>9,62; 18,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,31</t>
+          <t>8,22; 14,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,41</t>
+          <t>1,48; 4,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,3</t>
+          <t>4,15; 8,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 16,25</t>
+          <t>10,01; 15,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 18,13</t>
+          <t>10,39; 18,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 19,34</t>
+          <t>10,43; 18,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,86; 19,17</t>
+          <t>10,32; 19,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 51,13</t>
+          <t>17,46; 47,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,92</t>
+          <t>4,92; 10,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,87</t>
+          <t>3,14; 8,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,05</t>
+          <t>3,7; 9,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 25,5</t>
+          <t>10,87; 26,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,48; 13,42</t>
+          <t>8,55; 13,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 12,8</t>
+          <t>7,15; 12,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 13,15</t>
+          <t>7,7; 13,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 35,7</t>
+          <t>15,36; 36,04</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,8; 28,02</t>
+          <t>22,61; 27,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,89</t>
+          <t>17,9; 22,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,51; 24,36</t>
+          <t>19,45; 24,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,13; 35,05</t>
+          <t>18,92; 35,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,97; 26,0</t>
+          <t>20,94; 26,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,83; 18,31</t>
+          <t>13,63; 18,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 19,0</t>
+          <t>14,83; 19,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,47</t>
+          <t>15,31; 22,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,42; 26,13</t>
+          <t>22,42; 26,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 19,69</t>
+          <t>16,49; 19,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,64; 21,0</t>
+          <t>17,73; 21,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,87; 25,8</t>
+          <t>17,75; 25,91</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que no hacen ejercicio (tasa de respuesta: 99,44%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>77305</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>84118</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82542</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25352</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85074</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90579</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71321</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>30679</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>162380</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>174697</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>153863</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>56032</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>69793; 84576</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75688; 93683</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>72995; 90350</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19685; 30899</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>76465; 92958</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>80872; 99085</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>62266; 79596</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>25089; 36572</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>149537; 172107</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>161531; 188156</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>141054; 165689</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>48178; 64207</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>51694</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28105</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32373</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33644</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54371</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16172</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>34611</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>28912</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>106065</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>44276</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>66984</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>62556</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>41821; 62951</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20507; 38526</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>24671; 41704</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>25431; 44444</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>44163; 65144</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10494; 23223</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>26482; 43309</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>21216; 37532</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>91041; 119990</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>33673; 54682</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>54896; 79501</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>51960; 77869</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15600</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6523</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15035</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20884</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13705</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>28449</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>29306</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8499</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22533</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>49333</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10645; 22156</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3102; 11292</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9713; 22103</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14359; 29431</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8986; 19938</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>632; 5412</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4024; 12601</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>20356; 39389</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>22054; 37761</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4641; 14714</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15605; 31450</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>38503; 60905</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>27131</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24705</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24415</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>75515</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15722</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9718</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10975</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>47461</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>42853</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>34424</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35390</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>122976</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>20171; 36649</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17879; 32329</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>17816; 32922</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>48084; 130892</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10143; 21906</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5645; 15869</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6417; 16815</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>33201; 82439</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>34227; 54357</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>25109; 43184</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>26624; 46112</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>89224; 209379</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>171730</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143451</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>154366</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155395</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>135501</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>340603</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>261896</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>278770</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>290896</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>153497; 189808</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>126335; 161135</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>136754; 171778</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>125608; 237866</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>151063; 188270</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>101268; 134647</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>109816; 142331</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>116013; 169253</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>313924; 366474</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>238919; 285448</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>255880; 304123</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>252371; 368345</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP24_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,74; 79,66</t>
+          <t>65,35; 79,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,62; 65,14</t>
+          <t>52,09; 65,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,73; 68,98</t>
+          <t>56,32; 69,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35,15; 55,18</t>
+          <t>34,76; 55,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,71; 77,45</t>
+          <t>63,86; 76,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,13; 71,22</t>
+          <t>58,78; 72,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,2; 65,45</t>
+          <t>51,54; 65,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,84; 62,44</t>
+          <t>42,32; 62,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,11; 76,09</t>
+          <t>66,62; 76,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,09; 66,5</t>
+          <t>57,0; 66,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,84; 65,59</t>
+          <t>56,35; 65,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,05; 56,04</t>
+          <t>42,27; 56,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 25,01</t>
+          <t>16,25; 24,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 16,45</t>
+          <t>8,78; 15,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 19,81</t>
+          <t>11,5; 19,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,96; 27,9</t>
+          <t>15,98; 28,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,4; 25,67</t>
+          <t>17,45; 25,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,7</t>
+          <t>3,95; 9,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 16,78</t>
+          <t>9,88; 16,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 20,61</t>
+          <t>11,82; 20,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 23,74</t>
+          <t>18,15; 23,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,91</t>
+          <t>6,73; 11,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,72; 16,97</t>
+          <t>11,9; 17,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,22; 22,81</t>
+          <t>14,77; 22,24</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 17,46</t>
+          <t>8,1; 17,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,22</t>
+          <t>2,08; 7,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 11,7</t>
+          <t>5,23; 11,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,0</t>
+          <t>8,3; 16,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 14,09</t>
+          <t>6,18; 14,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,45</t>
+          <t>0,4; 3,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,72</t>
+          <t>2,05; 6,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 18,62</t>
+          <t>9,2; 18,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 14,07</t>
+          <t>8,48; 14,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,7</t>
+          <t>1,51; 4,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,35</t>
+          <t>4,26; 8,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 15,83</t>
+          <t>10,03; 16,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 18,88</t>
+          <t>10,61; 18,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 18,87</t>
+          <t>10,57; 19,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,32; 19,07</t>
+          <t>10,02; 18,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,46; 47,52</t>
+          <t>17,34; 49,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,63</t>
+          <t>5,09; 11,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,82</t>
+          <t>2,9; 8,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,7</t>
+          <t>3,24; 9,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,87; 26,99</t>
+          <t>11,07; 26,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,55; 13,58</t>
+          <t>8,38; 13,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 12,29</t>
+          <t>7,51; 13,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 13,33</t>
+          <t>7,8; 13,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,36; 36,04</t>
+          <t>15,55; 34,52</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,61; 27,96</t>
+          <t>22,76; 27,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,9; 22,83</t>
+          <t>17,86; 22,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 24,43</t>
+          <t>19,44; 24,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,92; 35,83</t>
+          <t>18,78; 34,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,94; 26,1</t>
+          <t>20,85; 25,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,63; 18,12</t>
+          <t>13,65; 18,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 19,22</t>
+          <t>14,58; 18,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,34</t>
+          <t>15,28; 22,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,42; 26,17</t>
+          <t>22,45; 26,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,49; 19,7</t>
+          <t>16,42; 19,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,73; 21,07</t>
+          <t>17,7; 20,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,75; 25,91</t>
+          <t>17,68; 25,51</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69793; 84576</t>
+          <t>69378; 83945</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>75688; 93683</t>
+          <t>74920; 93752</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72995; 90350</t>
+          <t>73770; 91475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19685; 30899</t>
+          <t>19464; 30929</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76465; 92958</t>
+          <t>76652; 92143</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80872; 99085</t>
+          <t>81772; 100521</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62266; 79596</t>
+          <t>62682; 79517</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25089; 36572</t>
+          <t>24784; 36710</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149537; 172107</t>
+          <t>150690; 172855</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161531; 188156</t>
+          <t>161292; 188485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>141054; 165689</t>
+          <t>142340; 165739</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48178; 64207</t>
+          <t>48429; 64580</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41821; 62951</t>
+          <t>40898; 62328</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20507; 38526</t>
+          <t>20567; 37407</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24671; 41704</t>
+          <t>24211; 41074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25431; 44444</t>
+          <t>25463; 45020</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44163; 65144</t>
+          <t>44269; 64353</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10494; 23223</t>
+          <t>10557; 24136</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26482; 43309</t>
+          <t>25503; 43165</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21216; 37532</t>
+          <t>21525; 38030</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91041; 119990</t>
+          <t>91747; 120196</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33673; 54682</t>
+          <t>33715; 55758</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54896; 79501</t>
+          <t>55774; 80074</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51960; 77869</t>
+          <t>50409; 75926</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10645; 22156</t>
+          <t>10274; 22175</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3102; 11292</t>
+          <t>3246; 11664</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9713; 22103</t>
+          <t>9886; 22645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14359; 29431</t>
+          <t>14360; 29329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8986; 19938</t>
+          <t>8753; 20038</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>632; 5412</t>
+          <t>632; 4748</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4024; 12601</t>
+          <t>3850; 12539</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20356; 39389</t>
+          <t>19460; 39250</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22054; 37761</t>
+          <t>22757; 38069</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4641; 14714</t>
+          <t>4727; 13842</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15605; 31450</t>
+          <t>16026; 30911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38503; 60905</t>
+          <t>38591; 63543</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20171; 36649</t>
+          <t>20595; 36130</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17879; 32329</t>
+          <t>18106; 33809</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17816; 32922</t>
+          <t>17291; 32179</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48084; 130892</t>
+          <t>47751; 135168</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10143; 21906</t>
+          <t>10488; 23307</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5645; 15869</t>
+          <t>5222; 16180</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6417; 16815</t>
+          <t>5623; 17129</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33201; 82439</t>
+          <t>33820; 79700</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34227; 54357</t>
+          <t>33518; 54064</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25109; 43184</t>
+          <t>26382; 45861</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26624; 46112</t>
+          <t>26976; 46537</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89224; 209379</t>
+          <t>90361; 200561</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>153497; 189808</t>
+          <t>154519; 189953</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126335; 161135</t>
+          <t>126031; 160032</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136754; 171778</t>
+          <t>136692; 172716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125608; 237866</t>
+          <t>124635; 229313</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>151063; 188270</t>
+          <t>150375; 187450</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>101268; 134647</t>
+          <t>101381; 136456</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>109816; 142331</t>
+          <t>108004; 139898</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>116013; 169253</t>
+          <t>115769; 168429</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>313924; 366474</t>
+          <t>314300; 366319</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>238919; 285448</t>
+          <t>237913; 284186</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>255880; 304123</t>
+          <t>255509; 302504</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>252371; 368345</t>
+          <t>251372; 362673</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70,88%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>65,11%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>58,64%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52,34%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>72,81%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>58,49%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>63,02%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>70,88%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,64%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,35; 79,07</t>
+          <t>63,78; 77,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,09; 65,18</t>
+          <t>58,31; 71,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,32; 69,84</t>
+          <t>51,55; 65,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,76; 55,23</t>
+          <t>42,58; 62,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>63,86; 76,77</t>
+          <t>65,85; 79,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,78; 72,26</t>
+          <t>51,23; 65,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,54; 65,38</t>
+          <t>56,43; 69,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,32; 62,68</t>
+          <t>33,17; 51,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,62; 76,42</t>
+          <t>66,77; 76,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,0; 66,62</t>
+          <t>56,69; 65,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,35; 65,61</t>
+          <t>55,6; 65,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,27; 56,37</t>
+          <t>40,63; 54,78</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>20,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>12,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,38%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,25; 24,76</t>
+          <t>17,56; 25,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 15,97</t>
+          <t>3,96; 8,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 19,51</t>
+          <t>9,97; 16,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,98; 28,26</t>
+          <t>11,08; 19,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,45; 25,36</t>
+          <t>16,77; 25,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,04</t>
+          <t>8,53; 16,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 16,73</t>
+          <t>11,82; 19,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 20,89</t>
+          <t>13,3; 22,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 23,78</t>
+          <t>18,13; 24,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 11,13</t>
+          <t>6,87; 11,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,9; 17,09</t>
+          <t>11,66; 16,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,77; 22,24</t>
+          <t>13,1; 19,67</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12,29%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,17%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 17,47</t>
+          <t>6,46; 14,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,46</t>
+          <t>0,4; 3,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 11,99</t>
+          <t>2,22; 6,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 16,95</t>
+          <t>8,49; 16,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 14,16</t>
+          <t>7,95; 17,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,03</t>
+          <t>2,08; 7,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,69</t>
+          <t>4,96; 11,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 18,55</t>
+          <t>8,4; 17,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 14,18</t>
+          <t>8,1; 14,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,42</t>
+          <t>1,47; 4,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,21</t>
+          <t>4,2; 8,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 16,52</t>
+          <t>9,4; 15,5</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,98%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14,14%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 18,61</t>
+          <t>5,01; 10,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,57; 19,73</t>
+          <t>3,03; 8,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 18,64</t>
+          <t>3,52; 10,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,34; 49,07</t>
+          <t>10,15; 22,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,31</t>
+          <t>10,15; 18,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,99</t>
+          <t>10,57; 19,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,88</t>
+          <t>9,86; 19,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 26,09</t>
+          <t>13,16; 21,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 13,51</t>
+          <t>8,48; 13,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 13,06</t>
+          <t>7,42; 12,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 13,45</t>
+          <t>7,8; 13,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 34,52</t>
+          <t>12,67; 20,77</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>25,29%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>20,33%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>21,96%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,76; 27,98</t>
+          <t>20,97; 26,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,86; 22,68</t>
+          <t>13,83; 18,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 24,57</t>
+          <t>14,58; 19,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,78; 34,54</t>
+          <t>14,19; 20,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,85; 25,99</t>
+          <t>22,8; 28,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,65; 18,37</t>
+          <t>18,08; 22,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 18,89</t>
+          <t>19,51; 24,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,23</t>
+          <t>15,46; 20,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,45; 26,16</t>
+          <t>22,42; 26,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 19,62</t>
+          <t>16,22; 19,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,7; 20,96</t>
+          <t>17,64; 21,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,68; 25,51</t>
+          <t>15,43; 19,39</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>50</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85074</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>90579</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71321</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25257</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>77305</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>84118</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>82542</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25352</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>85074</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90579</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71321</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>21400</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56032</t>
+          <t>46657</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69378; 83945</t>
+          <t>76550; 92782</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74920; 93752</t>
+          <t>81120; 99787</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73770; 91475</t>
+          <t>62699; 79920</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19464; 30929</t>
+          <t>20547; 29963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76652; 92143</t>
+          <t>69914; 84192</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81772; 100521</t>
+          <t>73684; 93655</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62682; 79517</t>
+          <t>73921; 90850</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24784; 36710</t>
+          <t>16844; 26175</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>150690; 172855</t>
+          <t>151039; 172449</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161292; 188485</t>
+          <t>160407; 186443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>142340; 165739</t>
+          <t>140459; 165983</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>48429; 64580</t>
+          <t>40238; 54249</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16172</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34611</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23667</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>51694</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>28105</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>32373</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33644</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>54371</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16172</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34611</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62556</t>
+          <t>49644</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40898; 62328</t>
+          <t>44548; 65745</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20567; 37407</t>
+          <t>10582; 23633</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24211; 41074</t>
+          <t>25725; 42797</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25463; 45020</t>
+          <t>17407; 31069</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44269; 64353</t>
+          <t>42207; 62996</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10557; 24136</t>
+          <t>19985; 37735</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25503; 43165</t>
+          <t>24885; 40806</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21525; 38030</t>
+          <t>19356; 32964</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91747; 120196</t>
+          <t>91643; 121911</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33715; 55758</t>
+          <t>34414; 55137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55774; 80074</t>
+          <t>54632; 79213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50409; 75926</t>
+          <t>39650; 59552</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13705</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24420</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>15600</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6523</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>15035</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20884</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13705</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7498</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49333</t>
+          <t>45874</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10274; 22175</t>
+          <t>9147; 19926</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3246; 11664</t>
+          <t>634; 5295</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9886; 22645</t>
+          <t>4155; 12973</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14360; 29329</t>
+          <t>16911; 33569</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8753; 20038</t>
+          <t>10093; 21865</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>632; 4748</t>
+          <t>3250; 11606</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3850; 12539</t>
+          <t>9360; 21656</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19460; 39250</t>
+          <t>14669; 30962</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22757; 38069</t>
+          <t>21747; 38408</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4727; 13842</t>
+          <t>4602; 13817</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16026; 30911</t>
+          <t>15801; 31245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38591; 63543</t>
+          <t>35153; 57936</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15722</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9718</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10975</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>27131</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>24705</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>24415</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>75515</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15722</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9718</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10975</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>47461</t>
+          <t>43254</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>122976</t>
+          <t>85255</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20595; 36130</t>
+          <t>10314; 22502</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18106; 33809</t>
+          <t>5453; 15958</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17291; 32179</t>
+          <t>6097; 17430</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47751; 135168</t>
+          <t>29698; 65907</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10488; 23307</t>
+          <t>19706; 35184</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5222; 16180</t>
+          <t>18118; 33137</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5623; 17129</t>
+          <t>17016; 33084</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33820; 79700</t>
+          <t>33760; 56351</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33518; 54064</t>
+          <t>33933; 53704</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26382; 45861</t>
+          <t>26071; 44949</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26976; 46537</t>
+          <t>26986; 45487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90361; 200561</t>
+          <t>69574; 114060</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>168873</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>118446</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124404</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>171730</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>143451</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>154366</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>168873</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>118446</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>124404</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>154519; 189953</t>
+          <t>151269; 187574</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>126031; 160032</t>
+          <t>102726; 136006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136692; 172716</t>
+          <t>107953; 140703</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124635; 229313</t>
+          <t>98906; 144738</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>150375; 187450</t>
+          <t>154794; 190240</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>101381; 136456</t>
+          <t>127592; 161534</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108004; 139898</t>
+          <t>137167; 171263</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115769; 168429</t>
+          <t>97037; 128550</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>314300; 366319</t>
+          <t>313929; 365840</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237913; 284186</t>
+          <t>235037; 285202</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>255509; 302504</t>
+          <t>254577; 303220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>251372; 362673</t>
+          <t>204352; 256861</t>
         </is>
       </c>
     </row>
